--- a/test-files/graph-tests/check-self-referential-widths.xlsx
+++ b/test-files/graph-tests/check-self-referential-widths.xlsx
@@ -1,97 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="124226"/>
-  <bookViews>
-    <workbookView xWindow="-75" yWindow="2805" windowWidth="27660" windowHeight="8580"/>
-  </bookViews>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <sheets>
     <sheet name="network_optimized_weights" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="22">
-  <si>
-    <t>rows genes affected/cols genes controlling</t>
-  </si>
-  <si>
-    <t>ACE2</t>
-  </si>
-  <si>
-    <t>AFT2</t>
-  </si>
-  <si>
-    <t>CIN5</t>
-  </si>
-  <si>
-    <t>FHL1</t>
-  </si>
-  <si>
-    <t>FKH2</t>
-  </si>
-  <si>
-    <t>GLN3</t>
-  </si>
-  <si>
-    <t>HAP5</t>
-  </si>
-  <si>
-    <t>HMO1</t>
-  </si>
-  <si>
-    <t>HOT1</t>
-  </si>
-  <si>
-    <t>MAL33</t>
-  </si>
-  <si>
-    <t>MBP1</t>
-  </si>
-  <si>
-    <t>MGA2</t>
-  </si>
-  <si>
-    <t>MSS11</t>
-  </si>
-  <si>
-    <t>PHD1</t>
-  </si>
-  <si>
-    <t>SKN7</t>
-  </si>
-  <si>
-    <t>SKO1</t>
-  </si>
-  <si>
-    <t>SMP1</t>
-  </si>
-  <si>
-    <t>SWI4</t>
-  </si>
-  <si>
-    <t>SWI6</t>
-  </si>
-  <si>
-    <t>YAP6</t>
-  </si>
-  <si>
-    <t>ZAP1</t>
-  </si>
-</sst>
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
-      <sz val="10"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -115,18 +65,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -275,20 +220,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -410,87 +351,125 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:V22"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>1</v>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>cols regulators/rows targets</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ACE2</v>
+      </c>
+      <c r="C1" t="str">
+        <v>AFT2</v>
+      </c>
+      <c r="D1" t="str">
+        <v>CIN5</v>
+      </c>
+      <c r="E1" t="str">
+        <v>FHL1</v>
+      </c>
+      <c r="F1" t="str">
+        <v>FKH2</v>
+      </c>
+      <c r="G1" t="str">
+        <v>GLN3</v>
+      </c>
+      <c r="H1" t="str">
+        <v>HAP5</v>
+      </c>
+      <c r="I1" t="str">
+        <v>HMO1</v>
+      </c>
+      <c r="J1" t="str">
+        <v>HOT1</v>
+      </c>
+      <c r="K1" t="str">
+        <v>MAL33</v>
+      </c>
+      <c r="L1" t="str">
+        <v>MBP1</v>
+      </c>
+      <c r="M1" t="str">
+        <v>MGA2</v>
+      </c>
+      <c r="N1" t="str">
+        <v>MSS11</v>
+      </c>
+      <c r="O1" t="str">
+        <v>PHD1</v>
+      </c>
+      <c r="P1" t="str">
+        <v>SKN7</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>SKO1</v>
+      </c>
+      <c r="R1" t="str">
+        <v>SMP1</v>
+      </c>
+      <c r="S1" t="str">
+        <v>SWI4</v>
+      </c>
+      <c r="T1" t="str">
+        <v>SWI6</v>
+      </c>
+      <c r="U1" t="str">
+        <v>YAP6</v>
+      </c>
+      <c r="V1" t="str">
+        <v>ZAP1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>ACE2</v>
       </c>
       <c r="B2">
         <v>4.5</v>
@@ -556,9 +535,9 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
-        <v>2</v>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>AFT2</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -624,9 +603,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>3</v>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>CIN5</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -692,9 +671,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>4</v>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>FHL1</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -760,9 +739,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>5</v>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>FKH2</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -828,9 +807,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>6</v>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>GLN3</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -896,9 +875,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>7</v>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>HAP5</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -964,9 +943,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>8</v>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>HMO1</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -1032,9 +1011,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>9</v>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>HOT1</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1100,9 +1079,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>10</v>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>MAL33</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -1168,9 +1147,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>11</v>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>MBP1</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -1236,9 +1215,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>12</v>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>MGA2</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1304,9 +1283,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>13</v>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>MSS11</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -1372,9 +1351,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>14</v>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>PHD1</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -1440,9 +1419,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>15</v>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>SKN7</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -1508,9 +1487,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>16</v>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>SKO1</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -1576,9 +1555,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>17</v>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>SMP1</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -1644,9 +1623,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>18</v>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>SWI4</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1712,9 +1691,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>19</v>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SWI6</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1780,9 +1759,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>20</v>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>YAP6</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -1848,9 +1827,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>21</v>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>ZAP1</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1917,6 +1896,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:V22"/>
+  </ignoredErrors>
 </worksheet>
 </file>